--- a/exports/trend_1d/UNIONBANK_full_report.xlsx
+++ b/exports/trend_1d/UNIONBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q90"/>
+  <dimension ref="A1:U90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>12.78</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42032</v>
+        <v>42033</v>
       </c>
       <c r="H2" t="n">
-        <v>209.47</v>
+        <v>199.5</v>
       </c>
       <c r="I2" t="n">
         <v>207.307543785</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.41</v>
+        <v>-9.91</v>
       </c>
       <c r="L2" t="n">
-        <v>5.75</v>
+        <v>10.46</v>
       </c>
       <c r="M2" t="n">
         <v>0.91</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.34</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42136</v>
+        <v>42137</v>
       </c>
       <c r="H3" t="n">
-        <v>131.58</v>
+        <v>141.86</v>
       </c>
       <c r="I3" t="n">
         <v>137.088075736229</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K3" t="n">
-        <v>34.05</v>
+        <v>28.89</v>
       </c>
       <c r="L3" t="n">
         <v>4.73</v>
@@ -612,7 +647,7 @@
         <v>3.99</v>
       </c>
       <c r="N3" t="n">
-        <v>5.33</v>
+        <v>7.81</v>
       </c>
       <c r="O3" t="n">
         <v>-4.76</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>16.53</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42158</v>
+        <v>42159</v>
       </c>
       <c r="H4" t="n">
-        <v>149.23</v>
+        <v>142.52</v>
       </c>
       <c r="I4" t="n">
         <v>144.5751596237928</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2</v>
+        <v>0.47</v>
       </c>
       <c r="L4" t="n">
         <v>6.19</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>16.24</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42187</v>
+        <v>42188</v>
       </c>
       <c r="H5" t="n">
-        <v>141.24</v>
+        <v>148.58</v>
       </c>
       <c r="I5" t="n">
         <v>148.4479947031502</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9</v>
+        <v>-4.25</v>
       </c>
       <c r="L5" t="n">
         <v>5.34</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>16.02</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42209</v>
+        <v>42212</v>
       </c>
       <c r="H6" t="n">
-        <v>146.47</v>
+        <v>141.4</v>
       </c>
       <c r="I6" t="n">
         <v>144.4334673726838</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.42</v>
+        <v>-4.83</v>
       </c>
       <c r="L6" t="n">
         <v>5.47</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>13.62</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42215</v>
+        <v>42216</v>
       </c>
       <c r="H7" t="n">
-        <v>150.79</v>
+        <v>162.43</v>
       </c>
       <c r="I7" t="n">
         <v>160.6575019909936</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.64</v>
+        <v>-14.87</v>
       </c>
       <c r="L7" t="n">
-        <v>7.57</v>
+        <v>17.33</v>
       </c>
       <c r="M7" t="n">
         <v>0.74</v>
       </c>
       <c r="N7" t="n">
-        <v>7.32</v>
+        <v>7.72</v>
       </c>
       <c r="O7" t="n">
         <v>-3.46</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>17.33</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H8" t="n">
-        <v>184.42</v>
+        <v>159.53</v>
       </c>
       <c r="I8" t="n">
         <v>171.5336422167765</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>13.54</v>
+        <v>-1.79</v>
       </c>
       <c r="L8" t="n">
         <v>8.24</v>
       </c>
       <c r="M8" t="n">
-        <v>4.35</v>
+        <v>6.11</v>
       </c>
       <c r="N8" t="n">
-        <v>5.23</v>
+        <v>13.5</v>
       </c>
       <c r="O8" t="n">
         <v>7.72</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>27.54</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42394</v>
+        <v>42396</v>
       </c>
       <c r="H9" t="n">
-        <v>108.32</v>
+        <v>118.89</v>
       </c>
       <c r="I9" t="n">
         <v>117.2449838518892</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K9" t="n">
-        <v>32.1</v>
+        <v>25.47</v>
       </c>
       <c r="L9" t="n">
         <v>10.93</v>
@@ -954,7 +1061,7 @@
         <v>3.89</v>
       </c>
       <c r="N9" t="n">
-        <v>7.36</v>
+        <v>9.76</v>
       </c>
       <c r="O9" t="n">
         <v>-13.5</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>19.36</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42411</v>
+        <v>42412</v>
       </c>
       <c r="H10" t="n">
-        <v>107.76</v>
+        <v>100.01</v>
       </c>
       <c r="I10" t="n">
         <v>103.3344937582022</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.359999999999999</v>
+        <v>-15.88</v>
       </c>
       <c r="L10" t="n">
-        <v>10.31</v>
+        <v>19.44</v>
       </c>
       <c r="M10" t="n">
         <v>2.33</v>
       </c>
       <c r="N10" t="n">
-        <v>4.89</v>
+        <v>7.19</v>
       </c>
       <c r="O10" t="n">
         <v>9.76</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>26.75</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42447</v>
+        <v>42450</v>
       </c>
       <c r="H11" t="n">
-        <v>116.73</v>
+        <v>119.41</v>
       </c>
       <c r="I11" t="n">
         <v>118.9369541974035</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K11" t="n">
-        <v>-16.72</v>
+        <v>-19.4</v>
       </c>
       <c r="L11" t="n">
-        <v>18.46</v>
+        <v>20.48</v>
       </c>
       <c r="M11" t="n">
         <v>4.07</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>12.64</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42493</v>
+        <v>42494</v>
       </c>
       <c r="H12" t="n">
-        <v>113.35</v>
+        <v>107.2</v>
       </c>
       <c r="I12" t="n">
         <v>111.9013503781388</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.07</v>
+        <v>-10.23</v>
       </c>
       <c r="L12" t="n">
-        <v>5.86</v>
+        <v>10.62</v>
       </c>
       <c r="M12" t="n">
-        <v>0.61</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
         <v>6.02</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>15.96</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42528</v>
+        <v>42529</v>
       </c>
       <c r="H13" t="n">
-        <v>107.38</v>
+        <v>110.01</v>
       </c>
       <c r="I13" t="n">
         <v>108.1377718489504</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.17</v>
+        <v>-2.62</v>
       </c>
       <c r="L13" t="n">
         <v>5.43</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.01</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="H14" t="n">
-        <v>116.31</v>
+        <v>114.05</v>
       </c>
       <c r="I14" t="n">
         <v>114.3551552408939</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K14" t="n">
-        <v>5.73</v>
+        <v>3.67</v>
       </c>
       <c r="L14" t="n">
         <v>4.22</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>13.93</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42611</v>
+        <v>42612</v>
       </c>
       <c r="H15" t="n">
-        <v>122.84</v>
+        <v>129.51</v>
       </c>
       <c r="I15" t="n">
         <v>128.5368583584522</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.71</v>
+        <v>-13.56</v>
       </c>
       <c r="L15" t="n">
-        <v>10.5</v>
+        <v>14.78</v>
       </c>
       <c r="M15" t="n">
         <v>1.38</v>
       </c>
       <c r="N15" t="n">
-        <v>4.61</v>
+        <v>5.43</v>
       </c>
       <c r="O15" t="n">
         <v>-1.94</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.76</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42677</v>
+        <v>42678</v>
       </c>
       <c r="H16" t="n">
-        <v>125.38</v>
+        <v>122.46</v>
       </c>
       <c r="I16" t="n">
         <v>123.8146464635225</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.19</v>
+        <v>-5.44</v>
       </c>
       <c r="L16" t="n">
-        <v>6.52</v>
+        <v>6.64</v>
       </c>
       <c r="M16" t="n">
         <v>1.99</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>12.73</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H17" t="n">
-        <v>117.53</v>
+        <v>131.01</v>
       </c>
       <c r="I17" t="n">
         <v>129.6848887014417</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>4.03</v>
+        <v>-6.98</v>
       </c>
       <c r="L17" t="n">
-        <v>3.34</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>1.42</v>
+        <v>4.24</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>11.47</v>
       </c>
       <c r="O17" t="n">
         <v>-2.33</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>18.27</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42723</v>
+        <v>42724</v>
       </c>
       <c r="H18" t="n">
-        <v>122.09</v>
+        <v>118.14</v>
       </c>
       <c r="I18" t="n">
         <v>120.5842597241846</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.81</v>
+        <v>-9.82</v>
       </c>
       <c r="L18" t="n">
-        <v>7.56</v>
+        <v>10.43</v>
       </c>
       <c r="M18" t="n">
         <v>1.64</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>13.29</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H19" t="n">
-        <v>119.93</v>
+        <v>128.33</v>
       </c>
       <c r="I19" t="n">
         <v>124.2072776159013</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.52</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>3.78</v>
+        <v>11.53</v>
       </c>
       <c r="M19" t="n">
         <v>1.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
         <v>-3.24</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>12.52</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42776</v>
+        <v>42779</v>
       </c>
       <c r="H20" t="n">
-        <v>137.73</v>
+        <v>133.83</v>
       </c>
       <c r="I20" t="n">
         <v>136.1197098131036</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K20" t="n">
-        <v>7.32</v>
+        <v>4.29</v>
       </c>
       <c r="L20" t="n">
         <v>6.7</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>17.18</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42835</v>
+        <v>42836</v>
       </c>
       <c r="H21" t="n">
-        <v>142.71</v>
+        <v>146.05</v>
       </c>
       <c r="I21" t="n">
         <v>145.5790910223791</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.64</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>9.720000000000001</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.04</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H22" t="n">
-        <v>154.6</v>
+        <v>150.51</v>
       </c>
       <c r="I22" t="n">
         <v>153.8284551961014</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K22" t="n">
-        <v>5.85</v>
+        <v>3.05</v>
       </c>
       <c r="L22" t="n">
         <v>7.24</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>15.09</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42940</v>
+        <v>42941</v>
       </c>
       <c r="H23" t="n">
-        <v>144.4</v>
+        <v>148.11</v>
       </c>
       <c r="I23" t="n">
         <v>144.4855000306158</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K23" t="n">
-        <v>4.06</v>
+        <v>1.59</v>
       </c>
       <c r="L23" t="n">
         <v>3.21</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>9.26</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>42949</v>
+        <v>42950</v>
       </c>
       <c r="H24" t="n">
-        <v>137.59</v>
+        <v>131.53</v>
       </c>
       <c r="I24" t="n">
         <v>134.7584419225319</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.1</v>
+        <v>-11.19</v>
       </c>
       <c r="L24" t="n">
-        <v>7.64</v>
+        <v>12.24</v>
       </c>
       <c r="M24" t="n">
-        <v>0.32</v>
+        <v>1.37</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>4.4</v>
       </c>
       <c r="O24" t="n">
         <v>2.57</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>12.89</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H25" t="n">
-        <v>120.07</v>
+        <v>162.25</v>
       </c>
       <c r="I25" t="n">
         <v>125.0648943488227</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K25" t="n">
-        <v>8.710000000000001</v>
+        <v>-23.36</v>
       </c>
       <c r="L25" t="n">
-        <v>3.5</v>
+        <v>24.57</v>
       </c>
       <c r="M25" t="n">
-        <v>1.13</v>
+        <v>10.24</v>
       </c>
       <c r="N25" t="n">
-        <v>4.19</v>
+        <v>35.13</v>
       </c>
       <c r="O25" t="n">
         <v>-4.4</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>22.7</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43074</v>
+        <v>43075</v>
       </c>
       <c r="H26" t="n">
-        <v>148.02</v>
+        <v>142.38</v>
       </c>
       <c r="I26" t="n">
         <v>143.6252770197082</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K26" t="n">
-        <v>-8.77</v>
+        <v>-12.25</v>
       </c>
       <c r="L26" t="n">
         <v>18.42</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>14.54</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43306</v>
+        <v>43307</v>
       </c>
       <c r="H27" t="n">
-        <v>73.52</v>
+        <v>76.52</v>
       </c>
       <c r="I27" t="n">
         <v>75.70395572209635</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K27" t="n">
-        <v>48.36</v>
+        <v>46.26</v>
       </c>
       <c r="L27" t="n">
         <v>4.39</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>15.08</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43360</v>
+        <v>43361</v>
       </c>
       <c r="H28" t="n">
-        <v>73.94</v>
+        <v>66.94</v>
       </c>
       <c r="I28" t="n">
         <v>71.96205334063816</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.37</v>
+        <v>-12.52</v>
       </c>
       <c r="L28" t="n">
-        <v>7.29</v>
+        <v>13.32</v>
       </c>
       <c r="M28" t="n">
         <v>2.06</v>
       </c>
       <c r="N28" t="n">
-        <v>6.35</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O28" t="n">
         <v>4.08</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>20.43</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43402</v>
+        <v>43403</v>
       </c>
       <c r="H29" t="n">
-        <v>62.1</v>
+        <v>67.83</v>
       </c>
       <c r="I29" t="n">
         <v>65.50853861735844</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K29" t="n">
-        <v>7.23</v>
+        <v>-1.33</v>
       </c>
       <c r="L29" t="n">
         <v>10.1</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>21.41</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43486</v>
+        <v>43487</v>
       </c>
       <c r="H30" t="n">
-        <v>77.7</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="I30" t="n">
         <v>76.64334776975464</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K30" t="n">
-        <v>14.55</v>
+        <v>11.29</v>
       </c>
       <c r="L30" t="n">
         <v>9.289999999999999</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>15.42</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H31" t="n">
-        <v>69.09999999999999</v>
+        <v>72.39</v>
       </c>
       <c r="I31" t="n">
         <v>69.49402354054861</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K31" t="n">
-        <v>8.460000000000001</v>
+        <v>4.11</v>
       </c>
       <c r="L31" t="n">
         <v>3.3</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>15.33</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H32" t="n">
-        <v>82.12</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="I32" t="n">
         <v>78.43369271819411</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K32" t="n">
-        <v>13.44</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L32" t="n">
         <v>5.32</v>
@@ -2265,7 +2648,7 @@
         <v>1.67</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>4.76</v>
       </c>
       <c r="O32" t="n">
         <v>4.76</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.47</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43644</v>
+        <v>43647</v>
       </c>
       <c r="H33" t="n">
-        <v>72.76000000000001</v>
+        <v>75.06</v>
       </c>
       <c r="I33" t="n">
         <v>74.33545808758329</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K33" t="n">
-        <v>6.97</v>
+        <v>4.03</v>
       </c>
       <c r="L33" t="n">
         <v>4.21</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>13.53</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43658</v>
+        <v>43661</v>
       </c>
       <c r="H34" t="n">
-        <v>70.41</v>
+        <v>66.8</v>
       </c>
       <c r="I34" t="n">
         <v>68.33019771742683</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.2</v>
+        <v>-11</v>
       </c>
       <c r="L34" t="n">
-        <v>9.26</v>
+        <v>11.76</v>
       </c>
       <c r="M34" t="n">
         <v>0.75</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>16.1</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43769</v>
+        <v>43770</v>
       </c>
       <c r="H35" t="n">
-        <v>50.5</v>
+        <v>51.96</v>
       </c>
       <c r="I35" t="n">
         <v>50.66542325498101</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K35" t="n">
-        <v>24.4</v>
+        <v>22.22</v>
       </c>
       <c r="L35" t="n">
         <v>5.7</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>15.91</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43804</v>
+        <v>43805</v>
       </c>
       <c r="H36" t="n">
-        <v>51.25</v>
+        <v>48.25</v>
       </c>
       <c r="I36" t="n">
         <v>48.50222497424912</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.37</v>
+        <v>-7.14</v>
       </c>
       <c r="L36" t="n">
         <v>14.57</v>
@@ -2493,7 +2924,7 @@
         <v>1.42</v>
       </c>
       <c r="N36" t="n">
-        <v>5.36</v>
+        <v>5.85</v>
       </c>
       <c r="O36" t="n">
         <v>2.89</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>21.25</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H37" t="n">
-        <v>20.72</v>
+        <v>22.83</v>
       </c>
       <c r="I37" t="n">
         <v>20.83786476120688</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K37" t="n">
-        <v>57.06</v>
+        <v>52.68</v>
       </c>
       <c r="L37" t="n">
         <v>10.69</v>
@@ -2550,7 +2993,7 @@
         <v>8.84</v>
       </c>
       <c r="N37" t="n">
-        <v>9.41</v>
+        <v>10.18</v>
       </c>
       <c r="O37" t="n">
         <v>-5.85</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>7</v>
+      </c>
+      <c r="U37" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>16.7</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44039</v>
+        <v>44040</v>
       </c>
       <c r="H38" t="n">
-        <v>24.38</v>
+        <v>24.05</v>
       </c>
       <c r="I38" t="n">
         <v>24.1807355862364</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K38" t="n">
-        <v>6.79</v>
+        <v>5.34</v>
       </c>
       <c r="L38" t="n">
         <v>7.8</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.91</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44152</v>
+        <v>44153</v>
       </c>
       <c r="H39" t="n">
-        <v>20.01</v>
+        <v>20.72</v>
       </c>
       <c r="I39" t="n">
         <v>20.69388158637148</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K39" t="n">
-        <v>16.8</v>
+        <v>13.85</v>
       </c>
       <c r="L39" t="n">
         <v>12.68</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>9.58</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H40" t="n">
-        <v>25.84</v>
+        <v>23.72</v>
       </c>
       <c r="I40" t="n">
         <v>25.7213143316835</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K40" t="n">
-        <v>24.71</v>
+        <v>14.48</v>
       </c>
       <c r="L40" t="n">
         <v>3.67</v>
       </c>
       <c r="M40" t="n">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>4.14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O40" t="n">
         <v>3.55</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>19.11</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44207</v>
+        <v>44208</v>
       </c>
       <c r="H41" t="n">
-        <v>26.07</v>
+        <v>27.62</v>
       </c>
       <c r="I41" t="n">
         <v>27.28660118163647</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K41" t="n">
-        <v>-9.91</v>
+        <v>-16.44</v>
       </c>
       <c r="L41" t="n">
-        <v>16.06</v>
+        <v>18.42</v>
       </c>
       <c r="M41" t="n">
         <v>1.92</v>
       </c>
       <c r="N41" t="n">
-        <v>5.22</v>
+        <v>5.95</v>
       </c>
       <c r="O41" t="n">
         <v>-8.199999999999999</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>14.81</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44223</v>
+        <v>44224</v>
       </c>
       <c r="H42" t="n">
-        <v>24.85</v>
+        <v>24.33</v>
       </c>
       <c r="I42" t="n">
         <v>24.66396970440324</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>-10.03</v>
+        <v>-11.91</v>
       </c>
       <c r="L42" t="n">
-        <v>10.9</v>
+        <v>12.93</v>
       </c>
       <c r="M42" t="n">
-        <v>0.72</v>
+        <v>3.02</v>
       </c>
       <c r="N42" t="n">
         <v>2.64</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>12.83</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44228</v>
+        <v>44229</v>
       </c>
       <c r="H43" t="n">
-        <v>26.96</v>
+        <v>27.67</v>
       </c>
       <c r="I43" t="n">
         <v>27.45200159360891</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>-10.81</v>
+        <v>-13.73</v>
       </c>
       <c r="L43" t="n">
-        <v>11.39</v>
+        <v>17.76</v>
       </c>
       <c r="M43" t="n">
         <v>2.37</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.51</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H44" t="n">
-        <v>30.86</v>
+        <v>29.64</v>
       </c>
       <c r="I44" t="n">
         <v>30.113322714307</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K44" t="n">
-        <v>11.53</v>
+        <v>7.12</v>
       </c>
       <c r="L44" t="n">
         <v>1.88</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>19.57</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44328</v>
+        <v>44330</v>
       </c>
       <c r="H45" t="n">
-        <v>31.62</v>
+        <v>31.75</v>
       </c>
       <c r="I45" t="n">
         <v>31.67451691210449</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.68</v>
+        <v>-7.12</v>
       </c>
       <c r="L45" t="n">
-        <v>10.93</v>
+        <v>13.5</v>
       </c>
       <c r="M45" t="n">
         <v>2.7</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>13.42</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44342</v>
+        <v>44343</v>
       </c>
       <c r="H46" t="n">
-        <v>28.65</v>
+        <v>28.52</v>
       </c>
       <c r="I46" t="n">
         <v>28.61537209171564</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K46" t="n">
-        <v>-9.76</v>
+        <v>-10.17</v>
       </c>
       <c r="L46" t="n">
-        <v>10.05</v>
+        <v>10.49</v>
       </c>
       <c r="M46" t="n">
         <v>4.01</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>16.98</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44365</v>
+        <v>44368</v>
       </c>
       <c r="H47" t="n">
-        <v>32.13</v>
+        <v>34.01</v>
       </c>
       <c r="I47" t="n">
         <v>32.96839392020655</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K47" t="n">
-        <v>-12.66</v>
+        <v>-19.25</v>
       </c>
       <c r="L47" t="n">
-        <v>17.43</v>
+        <v>22.37</v>
       </c>
       <c r="M47" t="n">
         <v>2.83</v>
       </c>
       <c r="N47" t="n">
-        <v>4.48</v>
+        <v>5.85</v>
       </c>
       <c r="O47" t="n">
         <v>-0.45</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>17.47</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44404</v>
+        <v>44405</v>
       </c>
       <c r="H48" t="n">
-        <v>30.39</v>
+        <v>29.97</v>
       </c>
       <c r="I48" t="n">
         <v>29.97549758264718</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.64</v>
+        <v>-11.88</v>
       </c>
       <c r="L48" t="n">
-        <v>11.47</v>
+        <v>12.73</v>
       </c>
       <c r="M48" t="n">
         <v>3.21</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44454</v>
+        <v>44455</v>
       </c>
       <c r="H49" t="n">
-        <v>29.36</v>
+        <v>31.1</v>
       </c>
       <c r="I49" t="n">
         <v>30.57024345512411</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K49" t="n">
-        <v>2.04</v>
+        <v>-3.77</v>
       </c>
       <c r="L49" t="n">
         <v>10.34</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.49</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H50" t="n">
-        <v>40.68</v>
+        <v>37.81</v>
       </c>
       <c r="I50" t="n">
         <v>38.36178119535092</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K50" t="n">
-        <v>30.8</v>
+        <v>21.58</v>
       </c>
       <c r="L50" t="n">
         <v>8.17</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>24.2</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44588</v>
+        <v>44589</v>
       </c>
       <c r="H51" t="n">
-        <v>40.26</v>
+        <v>40.82</v>
       </c>
       <c r="I51" t="n">
         <v>40.67206606796372</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.48</v>
+        <v>-7.96</v>
       </c>
       <c r="L51" t="n">
         <v>14.55</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>12.35</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44613</v>
+        <v>44614</v>
       </c>
       <c r="H52" t="n">
-        <v>36.78</v>
+        <v>35.05</v>
       </c>
       <c r="I52" t="n">
         <v>36.34738173177529</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>-9.9</v>
+        <v>-14.14</v>
       </c>
       <c r="L52" t="n">
-        <v>12.08</v>
+        <v>17.83</v>
       </c>
       <c r="M52" t="n">
         <v>3.51</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>16.35</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H53" t="n">
-        <v>35.23</v>
+        <v>35.84</v>
       </c>
       <c r="I53" t="n">
         <v>35.78160320257904</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.51</v>
+        <v>-2.25</v>
       </c>
       <c r="L53" t="n">
         <v>4.94</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>11.34</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44679</v>
+        <v>44680</v>
       </c>
       <c r="H54" t="n">
-        <v>33.82</v>
+        <v>32.41</v>
       </c>
       <c r="I54" t="n">
         <v>33.40234228725874</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.64</v>
+        <v>-9.57</v>
       </c>
       <c r="L54" t="n">
-        <v>6</v>
+        <v>10.35</v>
       </c>
       <c r="M54" t="n">
         <v>1.55</v>
       </c>
       <c r="N54" t="n">
-        <v>2.99</v>
+        <v>4.17</v>
       </c>
       <c r="O54" t="n">
         <v>1.73</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>13.67</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44712</v>
+        <v>44713</v>
       </c>
       <c r="H55" t="n">
-        <v>32.18</v>
+        <v>33.02</v>
       </c>
       <c r="I55" t="n">
         <v>32.53740318232148</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K55" t="n">
-        <v>0.71</v>
+        <v>-1.88</v>
       </c>
       <c r="L55" t="n">
         <v>5.8</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>12.48</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H56" t="n">
-        <v>30.16</v>
+        <v>29.55</v>
       </c>
       <c r="I56" t="n">
         <v>29.67418722997032</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K56" t="n">
-        <v>-8.66</v>
+        <v>-10.51</v>
       </c>
       <c r="L56" t="n">
         <v>11.81</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>13.95</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44760</v>
+        <v>44761</v>
       </c>
       <c r="H57" t="n">
-        <v>31.52</v>
+        <v>32.23</v>
       </c>
       <c r="I57" t="n">
         <v>31.75067320834443</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.67</v>
+        <v>-9.07</v>
       </c>
       <c r="L57" t="n">
-        <v>8.390000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M57" t="n">
         <v>2.19</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.51</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H58" t="n">
-        <v>38.1</v>
+        <v>36.41</v>
       </c>
       <c r="I58" t="n">
         <v>37.3449829320068</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K58" t="n">
-        <v>18.21</v>
+        <v>12.97</v>
       </c>
       <c r="L58" t="n">
         <v>3.23</v>
@@ -3747,7 +4442,7 @@
         <v>3.85</v>
       </c>
       <c r="N58" t="n">
-        <v>3.67</v>
+        <v>4.44</v>
       </c>
       <c r="O58" t="n">
         <v>2.25</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>13.8</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44853</v>
+        <v>44854</v>
       </c>
       <c r="H59" t="n">
-        <v>40.02</v>
+        <v>41.01</v>
       </c>
       <c r="I59" t="n">
         <v>40.76735430063137</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K59" t="n">
-        <v>-9.91</v>
+        <v>-12.63</v>
       </c>
       <c r="L59" t="n">
-        <v>11.45</v>
+        <v>13.92</v>
       </c>
       <c r="M59" t="n">
         <v>2.42</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>11.26</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H60" t="n">
-        <v>72.91</v>
+        <v>68.16</v>
       </c>
       <c r="I60" t="n">
         <v>71.14443854758017</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K60" t="n">
-        <v>77.79000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="L60" t="n">
         <v>3.44</v>
@@ -3861,7 +4580,7 @@
         <v>1.06</v>
       </c>
       <c r="N60" t="n">
-        <v>6.19</v>
+        <v>6.51</v>
       </c>
       <c r="O60" t="n">
         <v>2.47</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>25.94</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45028</v>
+        <v>45029</v>
       </c>
       <c r="H61" t="n">
-        <v>60.12</v>
+        <v>62.1</v>
       </c>
       <c r="I61" t="n">
         <v>61.62037789825203</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K61" t="n">
-        <v>11.8</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L61" t="n">
         <v>14.13</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>12.34</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45055</v>
+        <v>45056</v>
       </c>
       <c r="H62" t="n">
-        <v>64.36</v>
+        <v>62.76</v>
       </c>
       <c r="I62" t="n">
         <v>63.3053541570864</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K62" t="n">
-        <v>3.64</v>
+        <v>1.06</v>
       </c>
       <c r="L62" t="n">
         <v>3.64</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>12.41</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45107</v>
+        <v>45110</v>
       </c>
       <c r="H63" t="n">
-        <v>64.5</v>
+        <v>66.98</v>
       </c>
       <c r="I63" t="n">
         <v>65.06240420183887</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.77</v>
+        <v>-6.72</v>
       </c>
       <c r="L63" t="n">
-        <v>4.56</v>
+        <v>7.04</v>
       </c>
       <c r="M63" t="n">
         <v>1.2</v>
       </c>
       <c r="N63" t="n">
-        <v>2.77</v>
+        <v>3.84</v>
       </c>
       <c r="O63" t="n">
         <v>-2.49</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.32</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45168</v>
+        <v>45169</v>
       </c>
       <c r="H64" t="n">
-        <v>78.31</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="I64" t="n">
         <v>77.35303541605761</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K64" t="n">
-        <v>16.92</v>
+        <v>15.44</v>
       </c>
       <c r="L64" t="n">
         <v>3.49</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>12.17</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45183</v>
+        <v>45184</v>
       </c>
       <c r="H65" t="n">
-        <v>85.40000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I65" t="n">
         <v>85.61508833332617</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K65" t="n">
-        <v>-10.45</v>
+        <v>-12.39</v>
       </c>
       <c r="L65" t="n">
-        <v>11.01</v>
+        <v>14.95</v>
       </c>
       <c r="M65" t="n">
         <v>1.62</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H66" t="n">
-        <v>91.64</v>
+        <v>85.87</v>
       </c>
       <c r="I66" t="n">
         <v>87.61984863774836</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K66" t="n">
-        <v>5.45</v>
+        <v>-1.19</v>
       </c>
       <c r="L66" t="n">
-        <v>1.19</v>
+        <v>3.35</v>
       </c>
       <c r="M66" t="n">
         <v>2.75</v>
       </c>
       <c r="N66" t="n">
-        <v>5.86</v>
+        <v>6.3</v>
       </c>
       <c r="O66" t="n">
         <v>1.76</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>16.91</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45242</v>
+        <v>45243</v>
       </c>
       <c r="H67" t="n">
-        <v>94.84</v>
+        <v>101.84</v>
       </c>
       <c r="I67" t="n">
         <v>96.77308758583682</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K67" t="n">
-        <v>-10.45</v>
+        <v>-18.6</v>
       </c>
       <c r="L67" t="n">
-        <v>12.86</v>
+        <v>19.32</v>
       </c>
       <c r="M67" t="n">
         <v>1.86</v>
       </c>
       <c r="N67" t="n">
-        <v>5.65</v>
+        <v>7.38</v>
       </c>
       <c r="O67" t="n">
         <v>-6.3</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>13.54</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="H68" t="n">
-        <v>136.79</v>
+        <v>133.13</v>
       </c>
       <c r="I68" t="n">
         <v>133.4525972946845</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K68" t="n">
-        <v>34.32</v>
+        <v>30.72</v>
       </c>
       <c r="L68" t="n">
         <v>7.47</v>
       </c>
       <c r="M68" t="n">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="N68" t="n">
         <v>6.27</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>6</v>
+      </c>
+      <c r="U68" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>10.4</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45408</v>
+        <v>45411</v>
       </c>
       <c r="H69" t="n">
-        <v>138.38</v>
+        <v>143.88</v>
       </c>
       <c r="I69" t="n">
         <v>141.6714409068536</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.94</v>
+        <v>-8.07</v>
       </c>
       <c r="L69" t="n">
-        <v>5.65</v>
+        <v>8.26</v>
       </c>
       <c r="M69" t="n">
         <v>1.45</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,25 +5249,25 @@
         <v>11.41</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="H70" t="n">
-        <v>130.03</v>
+        <v>124.77</v>
       </c>
       <c r="I70" t="n">
         <v>128.9913372421968</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K70" t="n">
-        <v>-9.630000000000001</v>
+        <v>-13.28</v>
       </c>
       <c r="L70" t="n">
-        <v>12.54</v>
+        <v>17.24</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="N70" t="n">
         <v>4.09</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>13.12</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45435</v>
+        <v>45436</v>
       </c>
       <c r="H71" t="n">
-        <v>139.99</v>
+        <v>143.65</v>
       </c>
       <c r="I71" t="n">
         <v>141.1401591027027</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K71" t="n">
-        <v>-12.2</v>
+        <v>-15.13</v>
       </c>
       <c r="L71" t="n">
-        <v>12.49</v>
+        <v>15.51</v>
       </c>
       <c r="M71" t="n">
         <v>1.11</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>12.18</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H72" t="n">
-        <v>156.33</v>
+        <v>127.2</v>
       </c>
       <c r="I72" t="n">
         <v>135.1870539519268</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K72" t="n">
-        <v>8.83</v>
+        <v>-11.45</v>
       </c>
       <c r="L72" t="n">
-        <v>4.9</v>
+        <v>13.41</v>
       </c>
       <c r="M72" t="n">
         <v>1.32</v>
       </c>
       <c r="N72" t="n">
-        <v>1.88</v>
+        <v>18.63</v>
       </c>
       <c r="O72" t="n">
         <v>2.61</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>31.61</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="H73" t="n">
-        <v>110.27</v>
+        <v>113.5</v>
       </c>
       <c r="I73" t="n">
         <v>112.2453152310497</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K73" t="n">
-        <v>13.31</v>
+        <v>10.77</v>
       </c>
       <c r="L73" t="n">
         <v>22.83</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>6</v>
+      </c>
+      <c r="U73" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>10.12</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H74" t="n">
-        <v>113.68</v>
+        <v>109.71</v>
       </c>
       <c r="I74" t="n">
         <v>112.1878520782187</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K74" t="n">
-        <v>0.16</v>
+        <v>-3.34</v>
       </c>
       <c r="L74" t="n">
         <v>7.3</v>
@@ -4659,7 +5546,7 @@
         <v>2.34</v>
       </c>
       <c r="N74" t="n">
-        <v>2.96</v>
+        <v>3.49</v>
       </c>
       <c r="O74" t="n">
         <v>2.93</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>11.14</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45687</v>
+        <v>45688</v>
       </c>
       <c r="H75" t="n">
-        <v>104.33</v>
+        <v>108.51</v>
       </c>
       <c r="I75" t="n">
         <v>108.5070556897958</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K75" t="n">
-        <v>4.9</v>
+        <v>1.09</v>
       </c>
       <c r="L75" t="n">
         <v>8.619999999999999</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>11.83</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="H76" t="n">
-        <v>111.3</v>
+        <v>108.58</v>
       </c>
       <c r="I76" t="n">
         <v>108.7781778904744</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K76" t="n">
-        <v>2.57</v>
+        <v>0.06</v>
       </c>
       <c r="L76" t="n">
         <v>7.68</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>13.96</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45790</v>
+        <v>45791</v>
       </c>
       <c r="H77" t="n">
-        <v>122.86</v>
+        <v>126.77</v>
       </c>
       <c r="I77" t="n">
         <v>123.738080548924</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>-13.15</v>
+        <v>-16.75</v>
       </c>
       <c r="L77" t="n">
-        <v>14.08</v>
+        <v>16.95</v>
       </c>
       <c r="M77" t="n">
         <v>2.52</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>12.65</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H78" t="n">
-        <v>135.4</v>
+        <v>131.23</v>
       </c>
       <c r="I78" t="n">
         <v>132.9721584280123</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K78" t="n">
-        <v>6.81</v>
+        <v>3.52</v>
       </c>
       <c r="L78" t="n">
         <v>2.84</v>
@@ -4887,7 +5822,7 @@
         <v>3.66</v>
       </c>
       <c r="N78" t="n">
-        <v>2.84</v>
+        <v>3.08</v>
       </c>
       <c r="O78" t="n">
         <v>3.18</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>10.4</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="H79" t="n">
-        <v>144.31</v>
+        <v>145.28</v>
       </c>
       <c r="I79" t="n">
         <v>144.8820207519655</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K79" t="n">
-        <v>-9.970000000000001</v>
+        <v>-10.71</v>
       </c>
       <c r="L79" t="n">
-        <v>10.97</v>
+        <v>11.26</v>
       </c>
       <c r="M79" t="n">
         <v>1.51</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H80" t="n">
-        <v>132.31</v>
+        <v>129.61</v>
       </c>
       <c r="I80" t="n">
         <v>132.1670058921554</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K80" t="n">
-        <v>-8.93</v>
+        <v>-10.79</v>
       </c>
       <c r="L80" t="n">
-        <v>9.109999999999999</v>
+        <v>11.01</v>
       </c>
       <c r="M80" t="n">
         <v>1.59</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H81" t="n">
-        <v>130.44</v>
+        <v>133.1</v>
       </c>
       <c r="I81" t="n">
         <v>131.8935622759305</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.64</v>
+        <v>-2.69</v>
       </c>
       <c r="L81" t="n">
         <v>3.83</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -5094,25 +6077,25 @@
         <v>7.22</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H82" t="n">
-        <v>183.24</v>
+        <v>173.92</v>
       </c>
       <c r="I82" t="n">
         <v>179.7255319322412</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K82" t="n">
-        <v>37.67</v>
+        <v>30.67</v>
       </c>
       <c r="L82" t="n">
         <v>2.28</v>
       </c>
       <c r="M82" t="n">
-        <v>3.57</v>
+        <v>3.79</v>
       </c>
       <c r="N82" t="n">
         <v>6.3</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>7</v>
+      </c>
+      <c r="U82" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -5151,22 +6146,22 @@
         <v>11.69</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="H83" t="n">
-        <v>185.89</v>
+        <v>188.48</v>
       </c>
       <c r="I83" t="n">
         <v>186.0399367153358</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K83" t="n">
-        <v>-6.88</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>7.9</v>
+        <v>10.1</v>
       </c>
       <c r="M83" t="n">
         <v>4.73</v>
@@ -5181,7 +6176,19 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,25 +6215,25 @@
         <v>10.64</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H84" t="n">
-        <v>171.05</v>
+        <v>165.59</v>
       </c>
       <c r="I84" t="n">
         <v>168.4274409802039</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K84" t="n">
-        <v>-9.25</v>
+        <v>-12.14</v>
       </c>
       <c r="L84" t="n">
-        <v>10.12</v>
+        <v>12.82</v>
       </c>
       <c r="M84" t="n">
-        <v>0.23</v>
+        <v>1.62</v>
       </c>
       <c r="N84" t="n">
         <v>7.39</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5265,19 +6284,19 @@
         <v>13.5</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H85" t="n">
-        <v>165.67</v>
+        <v>168.77</v>
       </c>
       <c r="I85" t="n">
         <v>167.0793849084187</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.05</v>
+        <v>-1.92</v>
       </c>
       <c r="L85" t="n">
         <v>2.24</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,28 +6353,28 @@
         <v>9.33</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="H86" t="n">
-        <v>161.08</v>
+        <v>154.39</v>
       </c>
       <c r="I86" t="n">
         <v>159.413954476349</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K86" t="n">
-        <v>-4.56</v>
+        <v>-8.52</v>
       </c>
       <c r="L86" t="n">
-        <v>4.97</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M86" t="n">
-        <v>0.33</v>
+        <v>0.55</v>
       </c>
       <c r="N86" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="O86" t="n">
         <v>1.87</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>2</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -5379,22 +6422,22 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="H87" t="n">
-        <v>164.51</v>
+        <v>170.39</v>
       </c>
       <c r="I87" t="n">
         <v>168.6388783923491</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K87" t="n">
-        <v>-6.55</v>
+        <v>-10.36</v>
       </c>
       <c r="L87" t="n">
-        <v>7.2</v>
+        <v>10.6</v>
       </c>
       <c r="M87" t="n">
         <v>0.34</v>
@@ -5409,7 +6452,19 @@
         <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S87" t="b">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -5436,19 +6491,19 @@
         <v>10.84</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H88" t="n">
-        <v>178.1</v>
+        <v>175</v>
       </c>
       <c r="I88" t="n">
         <v>176.1657005303758</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K88" t="n">
-        <v>4.52</v>
+        <v>2.71</v>
       </c>
       <c r="L88" t="n">
         <v>4.62</v>
@@ -5466,7 +6521,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>3</v>
+      </c>
+      <c r="U88" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -5493,19 +6560,19 @@
         <v>9.17</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="H89" t="n">
-        <v>182</v>
+        <v>182.85</v>
       </c>
       <c r="I89" t="n">
         <v>182.6924328073468</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K89" t="n">
-        <v>-4</v>
+        <v>-4.49</v>
       </c>
       <c r="L89" t="n">
         <v>6.29</v>
@@ -5523,7 +6590,19 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5574,6 +6653,14 @@
       <c r="Q90" t="n">
         <v>5</v>
       </c>
+      <c r="R90" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10532,7 +11619,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47.2</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="6">
@@ -10542,7 +11629,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -10552,7 +11639,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
@@ -10562,7 +11649,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -10572,7 +11659,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56.5</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="10">
@@ -10582,7 +11669,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104.5</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="11">
@@ -10592,7 +11679,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -10602,7 +11689,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -10612,7 +11699,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="14">
@@ -10622,7 +11709,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.56</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="15">
@@ -10632,7 +11719,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.8</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="16">
@@ -10642,7 +11729,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.31</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="17">
@@ -10652,7 +11739,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>77.79000000000001</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="18">
@@ -10662,7 +11749,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.6</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="19">
@@ -10672,7 +11759,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.09</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="20">
@@ -10682,7 +11769,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.52</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="21">
@@ -10692,7 +11779,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.83</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="22">
@@ -10702,7 +11789,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
@@ -10712,7 +11799,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
@@ -10722,7 +11809,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="25">
@@ -10732,7 +11819,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.84</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="26">
@@ -10742,7 +11829,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.74</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="27">
@@ -10752,7 +11839,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.86</v>
+        <v>35.13</v>
       </c>
     </row>
     <row r="28">
@@ -10762,7 +11849,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29">
